--- a/docs/gods.xlsx
+++ b/docs/gods.xlsx
@@ -616,14 +616,14 @@
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>信力行为.类型 → deeds[].type；13 种：battle / damage / earn_money / spend_money / enter_node / event_choice / explore / heal / item_cycle / item_triggered / place_item / travel / vitality_lost</t>
+          <t>信力行为.类型 → deeds[].type；16 种：battle（by_type 按节点类型）/ damage / earn_money / spend_money / enter_node / event_choice / explore / heal / item_cycle / item_triggered / place_item / travel / vitality_lost / item_acquired / distinct_items_fired / first_place</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t>献祭 → offerings[]：tags / min_cells / exact_grade 任一命中即可；multiplier 默认 1；per_cell = 再乘格子数</t>
+          <t>献祭 → offerings[]：条件 tags（任一命中）/ min_cells / exact_grade / has_stat（显式写了这条属性，默认值不算），几条条件之间用「；」隔开、同时满足；multiplier 默认 1；per_cell = 再乘格子数</t>
         </is>
       </c>
     </row>
@@ -661,7 +661,7 @@
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>「数」列里的值是现在 JSON 或构件默认值；改数改这里，再同步 JSON。新效果 / 新行为要先加构件（脚本 + 注册表一行）。</t>
+          <t>所有数（阈值、给几点、每场上限、献祭倍率、转化概率）都是占位，按测试重新规划（104 一节；结算屏有「信力节奏」一行，开发版能导 CSV）。改数改这里，然后跑 tools/gods_xlsx_to_json.gd 同步 JSON、再跑 tools/import_content.gd；tools/test.sh 会对照这张表与 JSON。新效果 / 新行为要先加构件（脚本 + 注册表一行）。</t>
         </is>
       </c>
     </row>
@@ -1109,20 +1109,14 @@
           <t>游戏里既有（082 占位）</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I6" s="4" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="J6" s="4" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
+      <c r="H6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J6" s="4" t="n">
+        <v>80</v>
       </c>
       <c r="K6" s="4" t="n"/>
       <c r="L6" s="4" t="n"/>
@@ -1145,7 +1139,7 @@
       </c>
       <c r="R6" s="4" t="inlineStr">
         <is>
-          <t>占位：等级功能全在盾牌上</t>
+          <t>占位：阈值待测试定（先按主神量级填 25 / 80）；1 格护符暂无效果；等级功能在赐福的盾牌上</t>
         </is>
       </c>
     </row>
@@ -1181,20 +1175,14 @@
           <t>游戏里既有（082 占位）</t>
         </is>
       </c>
-      <c r="H7" s="4" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I7" s="4" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="J7" s="4" t="inlineStr">
-        <is>
-          <t>待定</t>
-        </is>
+      <c r="H7" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>25</v>
+      </c>
+      <c r="J7" s="4" t="n">
+        <v>80</v>
       </c>
       <c r="K7" s="4" t="n"/>
       <c r="L7" s="4" t="n"/>
@@ -1217,7 +1205,7 @@
       </c>
       <c r="R7" s="4" t="inlineStr">
         <is>
-          <t>占位：等级功能全在长弓上</t>
+          <t>占位：阈值待测试定（先按主神量级填 25 / 80）；1 格护符暂无效果；等级功能在赐福的长弓上</t>
         </is>
       </c>
     </row>
@@ -1245,7 +1233,7 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>皇帝暗中扶持的一神教，在无信的贫民、奴隶与行商之间传</t>
+          <t>皇帝暗中扶持的一神教，在无信的贫民、奴隶与行商之间传。概念暂不引入，只占位</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
@@ -1346,7 +1334,7 @@
     <row r="11">
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>神的信物必然保函一个1格的护符</t>
+          <t>规矩：每位神的信物必然包含一枚 1 格的护符（新教除外，占位）；导入器守</t>
         </is>
       </c>
     </row>
@@ -1361,7 +1349,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -1651,8 +1639,16 @@
           <t>技巧之神</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>item_acquired</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>{"tag": "metal", "per_cell": true, "amount": 3}</t>
+        </is>
+      </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
           <t>获得新的金属标签道具，格子*3点</t>
@@ -1671,8 +1667,16 @@
           <t>技巧之神</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>distinct_items_fired</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>{"tag": "weapon", "amount": 10, "cap": 50}</t>
+        </is>
+      </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
           <t>每场战斗中每种不同名字的武器首次被触发时，+10</t>
@@ -1693,8 +1697,16 @@
           <t>狩猎之神</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>battle</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>{"by_type": {"battle": 5, "elite": 20, "core": 50}}</t>
+        </is>
+      </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
           <t>进入普通战斗+5，精英战斗+20，BOSS战+50</t>
@@ -1713,8 +1725,16 @@
           <t>狩猎之神</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>first_place</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>{"tag": "trophy", "rarity_pow": true, "plus": 1}</t>
+        </is>
+      </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
           <t>每局游戏中首次将一种战利品置入背包时，根据稀有度增加2^稀有度等级+1</t>
@@ -1722,8 +1742,36 @@
       </c>
       <c r="F13" s="4" t="n"/>
     </row>
-    <row r="15" ht="256.5" customHeight="1">
-      <c r="A15" s="5" t="inlineStr">
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>church</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>新教</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>event_choice</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>{}</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>事件里选一个选项 +1（占位）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="256.5" customHeight="1"/>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>作者给的节奏（093 七）：前两场战斗到 1 级、4～6 个战斗节点到 2 级、小图一般升不到最高级、中图最后升到最高级；倍率、上限、阈值都是数据，不写死。</t>
         </is>
@@ -2186,7 +2234,11 @@
           <t>技巧之神</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>has_stat: crit_chance</t>
+        </is>
+      </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
           <t>带有暴击属性的道具</t>
@@ -2306,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G33"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2942,17 +2994,17 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>draw_is_win → overtime_regen（103）</t>
+          <t>overtime_regen</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>{"amount": 8}</t>
+          <t>{"stacks": 8}</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>现在：平局视为胜利。103（作者已定）：改为加时阶段（30 秒起）大量回血 —— 往回血轴加层，推荐 +8 / 秒，可调</t>
+          <t>加时阶段（30 秒起）大量回血：往回血轴加 8 层（每秒 +8，可调）；替换了 093 的「平局算胜」（103）</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -3162,58 +3214,74 @@
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>war</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>战争之神</t>
+          <t>技巧之神</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D26" s="4" t="n"/>
+      <c r="D26" s="4" t="inlineStr">
+        <is>
+          <t>（道具）</t>
+        </is>
+      </c>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>无（也没有信物，激活不了）</t>
-        </is>
-      </c>
-      <c r="G26" s="4" t="n"/>
+          <t>盾牌：护甲 +4 —— 功能在「技巧之神赐福的盾牌」的 faith_bonuses 上</t>
+        </is>
+      </c>
+      <c r="G26" s="4" t="inlineStr">
+        <is>
+          <t>道具按阶</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
         <is>
-          <t>war</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>战争之神</t>
+          <t>技巧之神</t>
         </is>
       </c>
       <c r="C27" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D27" s="4" t="n"/>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>（道具）</t>
+        </is>
+      </c>
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>无</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="n"/>
+          <t>盾牌：弹开更久（对手第一次攻击必被弹开）</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>道具按阶</t>
+        </is>
+      </c>
     </row>
     <row r="28" ht="27" customHeight="1">
       <c r="A28" s="4" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>hunt</t>
         </is>
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>技巧之神</t>
+          <t>狩猎之神</t>
         </is>
       </c>
       <c r="C28" s="4" t="n">
@@ -3227,7 +3295,7 @@
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>盾牌：护甲 +4 —— 功能在「技巧之神赐福的盾牌」的 faith_bonuses 上</t>
+          <t>长弓：伤害 +4 —— 功能在「狩猎之神赐福的长弓」上；描述里的「箭矢追踪、对兽类更佳」没有做</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -3239,12 +3307,12 @@
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>hunt</t>
         </is>
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>技巧之神</t>
+          <t>狩猎之神</t>
         </is>
       </c>
       <c r="C29" s="4" t="n">
@@ -3258,7 +3326,7 @@
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>盾牌：弹开更久（对手第一次攻击必被弹开）</t>
+          <t>长弓：伤害再 +15%</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -3270,110 +3338,48 @@
     <row r="30" ht="27" customHeight="1">
       <c r="A30" s="4" t="inlineStr">
         <is>
-          <t>hunt</t>
+          <t>church</t>
         </is>
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>狩猎之神</t>
+          <t>新教</t>
         </is>
       </c>
       <c r="C30" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="D30" s="4" t="inlineStr">
-        <is>
-          <t>（道具）</t>
-        </is>
-      </c>
+      <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>长弓：伤害 +4 —— 功能在「狩猎之神赐福的长弓」上；描述里的「箭矢追踪、对兽类更佳」没有做</t>
-        </is>
-      </c>
-      <c r="G30" s="4" t="inlineStr">
-        <is>
-          <t>道具按阶</t>
-        </is>
-      </c>
+          <t>作者定留空</t>
+        </is>
+      </c>
+      <c r="G30" s="4" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>hunt</t>
+          <t>church</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>狩猎之神</t>
+          <t>新教</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>（道具）</t>
-        </is>
-      </c>
+      <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>长弓：伤害再 +15%</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>道具按阶</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>新教</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D32" s="4" t="n"/>
-      <c r="E32" s="4" t="n"/>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
           <t>作者定留空</t>
         </is>
       </c>
-      <c r="G32" s="4" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>church</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>新教</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="D33" s="4" t="n"/>
-      <c r="E33" s="4" t="n"/>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>作者定留空</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3386,7 +3392,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3525,10 +3531,14 @@
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>1 阶：（备注为空，待填） | —</t>
-        </is>
-      </c>
-      <c r="G4" s="4" t="n"/>
+          <t>— | —</t>
+        </is>
+      </c>
+      <c r="G4" s="4" t="inlineStr">
+        <is>
+          <t>1 阶功能已移除（104）</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
@@ -3697,143 +3707,139 @@
       </c>
       <c r="G9" s="4" t="n"/>
     </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>charm_skill</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>技巧之神的护符</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>— | —</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1 格珍宝，暂无效果（104）</t>
+        </is>
+      </c>
+    </row>
     <row r="11">
-      <c r="A11" s="6" t="inlineStr">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>charm_hunt</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>狩猎之神的护符</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>hunt</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>— | —</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1 格珍宝，暂无效果（104）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="27" customHeight="1">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>赐福模板（FaithDef.blessings）</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="7" t="inlineStr">
+    <row r="14" ht="27" customHeight="1">
+      <c r="A14" s="7" t="inlineStr">
         <is>
           <t>神</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>圈哪些道具</t>
         </is>
       </c>
-      <c r="C12" s="7" t="inlineStr">
+      <c r="C14" s="7" t="inlineStr">
         <is>
           <t>名字前缀</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
+      <c r="D14" s="7" t="inlineStr">
         <is>
           <t>激活即（active）</t>
         </is>
       </c>
-      <c r="E12" s="7" t="inlineStr">
+      <c r="E14" s="7" t="inlineStr">
         <is>
           <t>按阶（tier）</t>
         </is>
       </c>
-      <c r="F12" s="7" t="inlineStr">
+      <c r="F14" s="7" t="inlineStr">
         <is>
           <t>按信力（scaled）</t>
         </is>
       </c>
-      <c r="G12" s="7" t="inlineStr">
+      <c r="G14" s="7" t="inlineStr">
         <is>
           <t>稀有度加 / 价值倍率</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="27" customHeight="1">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>蛮神</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr">
-        <is>
-          <t>tags: weapon</t>
-        </is>
-      </c>
-      <c r="C13" s="4" t="inlineStr">
-        <is>
-          <t>蛮神赐福的</t>
-        </is>
-      </c>
-      <c r="D13" s="4" t="inlineStr">
-        <is>
-          <t>伤害 +10%</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F13" s="4" t="inlineStr">
-        <is>
-          <t>每 50 信力伤害 +1，最多 6 份</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="inlineStr">
-        <is>
-          <t>+1 / ×1.5（默认）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="27" customHeight="1">
-      <c r="A14" s="4" t="inlineStr">
-        <is>
-          <t>日神</t>
-        </is>
-      </c>
-      <c r="B14" s="4" t="inlineStr">
-        <is>
-          <t>tags: metal</t>
-        </is>
-      </c>
-      <c r="C14" s="4" t="inlineStr">
-        <is>
-          <t>日神赐福的</t>
-        </is>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>急速 +5%</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>2 级：耐力消耗 −10%</t>
-        </is>
-      </c>
-      <c r="F14" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>+1 / ×1.5（默认）</t>
         </is>
       </c>
     </row>
     <row r="15" ht="40.5" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
         <is>
-          <t>自然之神</t>
+          <t>蛮神</t>
         </is>
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>tags: gear / armor / shield / nature</t>
+          <t>tags: weapon</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>自然之神赐福的</t>
+          <t>蛮神赐福的</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>生命 +3</t>
+          <t>伤害 +10%</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -3843,7 +3849,7 @@
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>每 50 信力护甲 +1，最多 5 份</t>
+          <t>每 50 信力伤害 +1，最多 6 份</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -3855,32 +3861,32 @@
     <row r="16" ht="40.5" customHeight="1">
       <c r="A16" s="4" t="inlineStr">
         <is>
-          <t>大地之神</t>
+          <t>日神</t>
         </is>
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>min_cells: 5</t>
+          <t>tags: metal</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>大地之神赐福的</t>
+          <t>日神赐福的</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>耐力上限 +5</t>
+          <t>急速 +5%</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
+          <t>2 级：耐力消耗 −10%</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
           <t>—</t>
-        </is>
-      </c>
-      <c r="F16" s="4" t="inlineStr">
-        <is>
-          <t>每 50 信力护甲 +1，最多 5 份</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -3892,35 +3898,109 @@
     <row r="17" ht="27" customHeight="1">
       <c r="A17" s="4" t="inlineStr">
         <is>
+          <t>自然之神</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>tags: gear / armor / shield / nature</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>自然之神赐福的</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>生命 +3</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>每 50 信力护甲 +1，最多 5 份</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>+1 / ×1.5（默认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>大地之神</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>min_cells: 5</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>大地之神赐福的</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>耐力上限 +5</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>每 50 信力护甲 +1，最多 5 份</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>+1 / ×1.5（默认）</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
           <t>战争 / 技巧 / 狩猎 / 新教</t>
         </is>
       </c>
-      <c r="B17" s="4" t="inlineStr">
+      <c r="B19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="C17" s="4" t="inlineStr">
+      <c r="C19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D17" s="4" t="inlineStr">
+      <c r="D19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E17" s="4" t="inlineStr">
+      <c r="E19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F17" s="4" t="inlineStr">
+      <c r="F19" s="4" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G17" s="4" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>没有赐福模板</t>
         </is>

--- a/docs/gods.xlsx
+++ b/docs/gods.xlsx
@@ -2666,7 +2666,7 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>开战随机 3 把武器火焰附魔：每击附带 max(3, 30% 武器伤害) 火焰</t>
+          <t>开战按本局种子随机 3 把武器火焰附魔：每击附带 max(3, 30% 武器伤害) 火焰</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
@@ -2696,12 +2696,12 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>{"max_times": 0}</t>
+          <t>{"max_times": 0, "axis": "fire_damage", "gains": []}</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>祈祷：局内永久火焰加成，第 n 次后 +10 × n^0.7 %，不限次</t>
+          <t>祈祷：局内永久的「炽烈」层数（每层火焰伤害 +3%，放大所有火焰来源）；每次给的层数 gains 为空 = 斐波那契 1/1/2/3/5/8…，累计 1/2/4/7/12/20…，不限次</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">

--- a/docs/gods.xlsx
+++ b/docs/gods.xlsx
@@ -2358,7 +2358,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G34"/>
+  <dimension ref="A1:G35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -2731,12 +2731,12 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>{"count": 0, "stamina_cost_percent": -20}</t>
+          <t>{"count": 0}</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>全部武器火焰附魔，获得耐力消耗减少的buff5层（等效于当前耐力消耗变为97%^5）</t>
+          <t>全部武器火焰附魔</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -2746,37 +2746,37 @@
       </c>
     </row>
     <row r="12" ht="27" customHeight="1">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" t="inlineStr">
         <is>
           <t>sun</t>
         </is>
       </c>
-      <c r="B12" s="4" t="inlineStr">
+      <c r="B12" t="inlineStr">
         <is>
           <t>日神</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="D12" s="4" t="inlineStr">
-        <is>
-          <t>extra_drop_by_node</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="inlineStr">
-        <is>
-          <t>{"by_type": {"battle": 3, "elite": 4, "core": 5}}</t>
-        </is>
-      </c>
-      <c r="F12" s="4" t="inlineStr">
-        <is>
-          <t>敌人必定额外掉一件：普通 3（紫）/ 精英 4（金）/ BOSS 5（红）</t>
-        </is>
-      </c>
-      <c r="G12" s="4" t="inlineStr">
-        <is>
-          <t>掉落</t>
+      <c r="C12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>axis_boost</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>{"axis": "stamina_cost", "stacks": 5}</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>开战获得 5 层「灵巧」：耐力消耗 ×97%^层数（5 层 ≈ ×85.9%）</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>编译期</t>
         </is>
       </c>
     </row>
@@ -2792,51 +2792,51 @@
         </is>
       </c>
       <c r="C13" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>extra_drop_by_node</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>{"by_type": {"battle": 3, "elite": 4, "core": 5}}</t>
+        </is>
+      </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>留空</t>
-        </is>
-      </c>
-      <c r="G13" s="4" t="n"/>
+          <t>敌人必定额外掉一件：普通 3（紫）/ 精英 4（金）/ BOSS 5（红）</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>掉落</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>自然之神</t>
+          <t>日神</t>
         </is>
       </c>
       <c r="C14" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="4" t="inlineStr">
-        <is>
-          <t>altar_bless</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="inlineStr">
-        <is>
-          <t>{"cost": 40}</t>
-        </is>
-      </c>
+        <v>5</v>
+      </c>
+      <c r="D14" s="4" t="n"/>
+      <c r="E14" s="4" t="n"/>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>神坛祈求赐福</t>
-        </is>
-      </c>
-      <c r="G14" s="4" t="inlineStr">
-        <is>
-          <t>神坛</t>
-        </is>
-      </c>
+          <t>留空</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="n"/>
     </row>
     <row r="15" ht="27" customHeight="1">
       <c r="A15" s="4" t="inlineStr">
@@ -2854,22 +2854,22 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>stat_mod</t>
+          <t>altar_bless</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>{"mods": [{"stat": "regen_hp", "flat": 1.0}]}</t>
+          <t>{"cost": 40}</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>开战每秒回血 +1</t>
+          <t>神坛祈求赐福</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>编译期基线</t>
+          <t>神坛</t>
         </is>
       </c>
     </row>
@@ -2885,26 +2885,26 @@
         </is>
       </c>
       <c r="C16" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>altar_food_vitality</t>
+          <t>stat_mod</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>{"per_food": 1, "max_per_altar": 3}</t>
+          <t>{"mods": [{"stat": "regen_hp", "flat": 1.0}]}</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>献祭食物时恢复体力：每件 +1，每个神坛最多 3</t>
+          <t>开战每秒回血 +1</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>神坛</t>
+          <t>编译期基线</t>
         </is>
       </c>
     </row>
@@ -2920,26 +2920,26 @@
         </is>
       </c>
       <c r="C17" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>food_shield</t>
+          <t>altar_food_vitality</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>{"base": 2, "per_rarity": 2}</t>
+          <t>{"per_food": 1, "max_per_altar": 3}</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>开战按食物给护盾：每件 2 + 2 × 稀有度</t>
+          <t>献祭食物时恢复体力：每件 +1，每个神坛最多 3</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>编译期</t>
+          <t>神坛</t>
         </is>
       </c>
     </row>
@@ -2955,26 +2955,26 @@
         </is>
       </c>
       <c r="C18" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>food_double</t>
+          <t>food_shield</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>{"factor": 2}</t>
+          <t>{"base": 2, "per_rarity": 2}</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>食物效果翻倍：战斗数值 ×2，献祭回体力也 ×2</t>
+          <t>开战按食物给护盾：每件 2 + 2 × 稀有度</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>编译期 + 神坛</t>
+          <t>编译期</t>
         </is>
       </c>
     </row>
@@ -2990,61 +2990,61 @@
         </is>
       </c>
       <c r="C19" s="4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>overtime_regen</t>
+          <t>food_double</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>{"stacks": 8}</t>
+          <t>{"factor": 2}</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>加时阶段（30 秒起）大量回血：往回血轴加 8 层（每秒 +8，可调）；替换了 093 的「平局算胜」（103）</t>
+          <t>食物效果翻倍：战斗数值 ×2，献祭回体力也 ×2</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>战斗规则</t>
+          <t>编译期 + 神坛</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
         <is>
-          <t>earth</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>大地之神</t>
+          <t>自然之神</t>
         </is>
       </c>
       <c r="C20" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>altar_bless</t>
+          <t>overtime_regen</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>{"cost": 40}</t>
+          <t>{"stacks": 8}</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>神坛祈求赐福</t>
+          <t>加时阶段（30 秒起）大量回血：往回血轴加 8 层（每秒 +8，可调）；替换了 093 的「平局算胜」（103）</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>神坛</t>
+          <t>战斗规则</t>
         </is>
       </c>
     </row>
@@ -3064,22 +3064,22 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>stat_mod</t>
+          <t>altar_bless</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>{"mods": [{"stat": "max_stamina", "flat": 20.0}]}</t>
+          <t>{"cost": 40}</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>开战耐力上限 +20</t>
+          <t>神坛祈求赐福</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>编译期基线</t>
+          <t>神坛</t>
         </is>
       </c>
     </row>
@@ -3095,26 +3095,26 @@
         </is>
       </c>
       <c r="C22" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>altar_train_board</t>
+          <t>stat_mod</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>{"rows": 1, "max_times": 0}</t>
+          <t>{"mods": [{"stat": "max_stamina", "flat": 20.0}]}</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>锻炼：棋盘每次 +1 行，不限次</t>
+          <t>开战耐力上限 +20</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>神坛特殊操作</t>
+          <t>编译期基线</t>
         </is>
       </c>
     </row>
@@ -3130,26 +3130,26 @@
         </is>
       </c>
       <c r="C23" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>gift_on_enter</t>
+          <t>altar_train_board</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>{"by_type": {"battle": ["weapon"], "elite": ["gear", "armor", "shield"], "event": ["sigil", "part"], "extract": [], "core": ["treasure"]}}</t>
+          <t>{"rows": 1, "max_times": 0}</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>头一回踩上一个点得到对应类型的道具（进暂存区）：战斗 → 武器；精英 → 防具；事件 → 符号 / 零件；撤离点 → 随机；BOSS → 珍宝</t>
+          <t>锻炼：棋盘每次 +1 行，不限次</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>踩点钩子</t>
+          <t>神坛特殊操作</t>
         </is>
       </c>
     </row>
@@ -3165,26 +3165,26 @@
         </is>
       </c>
       <c r="C24" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>altar_reshape_node</t>
+          <t>gift_on_enter</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>{"types": ["battle", "elite", "search", "event", "shop"]}</t>
+          <t>{"by_type": {"battle": ["weapon"], "elite": ["gear", "armor", "shield"], "event": ["sigil", "part"], "extract": [], "core": ["treasure"]}}</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>改造此点：把当前点改成别的类型，只在神坛、不限次</t>
+          <t>头一回踩上一个点得到对应类型的道具（进暂存区）：战斗 → 武器；精英 → 防具；事件 → 符号 / 零件；撤离点 → 随机；BOSS → 珍宝</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>神坛特殊操作</t>
+          <t>踩点钩子</t>
         </is>
       </c>
     </row>
@@ -3200,36 +3200,48 @@
         </is>
       </c>
       <c r="C25" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>altar_reshape_node</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>{"types": ["battle", "elite", "search", "event", "shop"]}</t>
+        </is>
+      </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>留空</t>
-        </is>
-      </c>
-      <c r="G25" s="4" t="n"/>
+          <t>改造此点：把当前点改成别的类型，只在神坛、不限次</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>神坛特殊操作</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
         <is>
-          <t>skill</t>
+          <t>earth</t>
         </is>
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>技巧之神</t>
+          <t>大地之神</t>
         </is>
       </c>
       <c r="C26" s="4" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>神坛祈求赐福</t>
+          <t>留空</t>
         </is>
       </c>
       <c r="G26" s="4" t="n"/>
@@ -3252,14 +3264,10 @@
       <c r="E27" s="4" t="n"/>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>开战时获得5层耐力消耗减少的buff（等于耐力消耗变为原本的97%^5）</t>
-        </is>
-      </c>
-      <c r="G27" s="4" t="inlineStr">
-        <is>
-          <t>编译期</t>
-        </is>
-      </c>
+          <t>神坛祈求赐福</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -3273,18 +3281,18 @@
         </is>
       </c>
       <c r="C28" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D28" s="4" t="n"/>
       <c r="E28" s="4" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>所有武器攻击后有50%概率发动一次不消耗耐力的追加攻击</t>
+          <t>开战时获得5层耐力消耗减少的buff（等于耐力消耗变为原本的97%^5）</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>编译期挂规则</t>
+          <t>编译期</t>
         </is>
       </c>
     </row>
@@ -3300,16 +3308,20 @@
         </is>
       </c>
       <c r="C29" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D29" s="4" t="n"/>
       <c r="E29" s="4" t="n"/>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>待定</t>
-        </is>
-      </c>
-      <c r="G29" s="4" t="n"/>
+          <t>所有武器攻击后有50%概率发动一次不消耗耐力的追加攻击</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>编译期挂规则</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -3323,7 +3335,7 @@
         </is>
       </c>
       <c r="C30" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D30" s="4" t="n"/>
       <c r="E30" s="4" t="n"/>
@@ -3337,22 +3349,22 @@
     <row r="31" ht="15" customHeight="1">
       <c r="A31" s="4" t="inlineStr">
         <is>
-          <t>hunt</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>狩猎之神</t>
+          <t>技巧之神</t>
         </is>
       </c>
       <c r="C31" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D31" s="4" t="n"/>
       <c r="E31" s="4" t="n"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>神坛祈求赐福</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="G31" s="4" t="n"/>
@@ -3375,7 +3387,7 @@
       <c r="E32" s="4" t="n"/>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>待定</t>
+          <t>神坛祈求赐福</t>
         </is>
       </c>
       <c r="G32" s="4" t="n"/>
@@ -3383,12 +3395,12 @@
     <row r="33" ht="27" customHeight="1">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>church</t>
+          <t>hunt</t>
         </is>
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>新教</t>
+          <t>狩猎之神</t>
         </is>
       </c>
       <c r="C33" s="4" t="n">
@@ -3398,7 +3410,7 @@
       <c r="E33" s="4" t="n"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>作者定留空</t>
+          <t>待定</t>
         </is>
       </c>
       <c r="G33" s="4" t="n"/>
@@ -3415,7 +3427,7 @@
         </is>
       </c>
       <c r="C34" s="4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D34" s="4" t="n"/>
       <c r="E34" s="4" t="n"/>
@@ -3425,6 +3437,29 @@
         </is>
       </c>
       <c r="G34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>church</t>
+        </is>
+      </c>
+      <c r="B35" s="4" t="inlineStr">
+        <is>
+          <t>新教</t>
+        </is>
+      </c>
+      <c r="C35" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="inlineStr">
+        <is>
+          <t>作者定留空</t>
+        </is>
+      </c>
+      <c r="G35" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/docs/gods.xlsx
+++ b/docs/gods.xlsx
@@ -1788,7 +1788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2252,30 +2252,30 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>hunt</t>
-        </is>
-      </c>
-      <c r="B17" s="9" t="inlineStr">
-        <is>
-          <t>狩猎之神</t>
-        </is>
-      </c>
-      <c r="C17" s="4" t="inlineStr">
-        <is>
-          <t>tags: flesh / bone</t>
-        </is>
-      </c>
-      <c r="D17" s="4" t="inlineStr">
-        <is>
-          <t>血肉/骨头</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>skill</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>技巧之神</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>tags: crafted</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>工艺品</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
         <v>5</v>
       </c>
-      <c r="F17" s="4" t="b">
+      <c r="F17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2292,16 +2292,16 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>tags: trophy</t>
+          <t>tags: flesh / bone</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>战利品</t>
+          <t>血肉/骨头</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="F18" s="4" t="b">
         <v>0</v>
@@ -2313,35 +2313,64 @@
           <t>hunt</t>
         </is>
       </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="B19" s="9" t="inlineStr">
         <is>
           <t>狩猎之神</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>tags: leather</t>
+          <t>tags: trophy</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>皮革</t>
+          <t>战利品</t>
         </is>
       </c>
       <c r="E19" s="4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="F19" s="4" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="21" ht="81" customHeight="1">
-      <c r="B21" s="8" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>hunt</t>
+        </is>
+      </c>
+      <c r="B20" s="10" t="inlineStr">
+        <is>
+          <t>狩猎之神</t>
+        </is>
+      </c>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>tags: leather</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>皮革</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>5</v>
+      </c>
+      <c r="F20" s="4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" ht="81" customHeight="1"/>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>备注:献祭只能提升当前激活神明的信力，比如激活日神时献祭金属无法提升技巧之神的信力</t>
         </is>
       </c>
-      <c r="C21" s="8" t="inlineStr">
+      <c r="C22" s="8" t="inlineStr">
         <is>
           <t>备注2：当一个献祭道具符合当前神明的多个tag时，同时获得多次信力。比如道具拥有骨制品+武器tag，献祭给蛮神获得（稀有度*5+稀有度*2）点信力</t>
         </is>

--- a/docs/gods.xlsx
+++ b/docs/gods.xlsx
@@ -1704,7 +1704,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>{"by_type": {"battle": 5, "elite": 20, "hunt": 30, "core": 50}}</t>
+          <t>{"by_type": {"battle": 5, "elite": 20, "hunter": 30, "core": 50}}</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">

--- a/docs/gods.xlsx
+++ b/docs/gods.xlsx
@@ -1331,6 +1331,7 @@
         </is>
       </c>
     </row>
+    <row r="10"/>
     <row r="11" ht="27" customHeight="1">
       <c r="N11" s="8" t="inlineStr">
         <is>
@@ -2462,7 +2463,7 @@
       </c>
       <c r="F2" s="4" t="inlineStr">
         <is>
-          <t>神坛祈求赐福：花 40 信力赐福包里最值钱的一件（各神都有）</t>
+          <t>可以在祭坛赐福武器：花 40 信力赐福包里最值钱的一件（各神都有；花多少只写在神坛按钮上）</t>
         </is>
       </c>
       <c r="G2" s="4" t="inlineStr">
@@ -2492,12 +2493,12 @@
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>{"min_percent": 10, "max_percent": 50}</t>
+          <t>{"hp_percent": 30, "base_percent": 10, "step": 50, "per": 5, "max_percent": 50}</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>低血增伤：所有伤害独立乘区，血越少加得越高，10%～50% 线性</t>
+          <t>生命值低于 30% 时，造成伤害提高 X%：X = 10 + ⌊信力/50⌋×5，最多 50（188 补充一，作者 10-18 改成门槛式、随信力）</t>
         </is>
       </c>
       <c r="G3" s="4" t="inlineStr">
@@ -2527,12 +2528,12 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>{"hp_cost": 5, "stamina_gain": 10, "haste_percent": 5, "min_hp_left": 5}</t>
+          <t>{"hp_cost": 5, "faith_gain": 20, "damage_percent": 5, "haste_percent": 5, "min_hp_left": 5}</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
         <is>
-          <t>献祭生命上限：−5 生命上限 → +10 耐力上限、+5% 急速，可多次，生命至少留 5</t>
+          <t>献祭 5 生命上限，二选一：+20 信力，或这局所有道具造成伤害 +5%、急速 +5%（可叠）；生命至少留 5（188 补充一，不再给耐力上限）</t>
         </is>
       </c>
       <c r="G4" s="4" t="inlineStr">
@@ -2562,12 +2563,12 @@
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>{"vitality_cost": 1, "types": ["elite"]}</t>
+          <t>{"vitality_cost": 1, "faith_cost": 30, "types": ["battle", "elite"]}</t>
         </is>
       </c>
       <c r="F5" s="4" t="inlineStr">
         <is>
-          <t>秒杀精英，耗 1 体力</t>
+          <t>战前准备：耗 1 体力或 30 信力立即击败非首领敌人（普通战斗与精英；188 补充一）</t>
         </is>
       </c>
       <c r="G5" s="4" t="inlineStr">
@@ -2597,12 +2598,12 @@
       </c>
       <c r="E6" s="4" t="inlineStr">
         <is>
-          <t>{"seconds": 10}</t>
+          <t>{"base_sec": 2, "step": 50, "per_sec": 1, "max_sec": 20}</t>
         </is>
       </c>
       <c r="F6" s="4" t="inlineStr">
         <is>
-          <t>不死：血归零后坚持 10 秒，耐力无限、受到的伤害照记；到期血还是 0 才倒；一场一次（103 的衰竭与它兼容）</t>
+          <t>在战斗中首次生命归零时持续战斗 X 秒：X = 2 + ⌊信力/50⌋，最多 20；耐力无限、受到的伤害照记；到期血还是 0 才倒；一场一次（188 补充一）</t>
         </is>
       </c>
       <c r="G6" s="4" t="inlineStr">
@@ -3886,6 +3887,7 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>

--- a/docs/gods.xlsx
+++ b/docs/gods.xlsx
@@ -992,7 +992,7 @@
       </c>
       <c r="O4" s="4" t="inlineStr">
         <is>
-          <t>防具（gear / armor / shield）与自然道具 → 自然之神赐福的</t>
+          <t>防具（armor / shield）与自然道具 → 自然之神赐福的</t>
         </is>
       </c>
       <c r="P4" s="4" t="n">
@@ -1331,7 +1331,6 @@
         </is>
       </c>
     </row>
-    <row r="10"/>
     <row r="11" ht="27" customHeight="1">
       <c r="N11" s="8" t="inlineStr">
         <is>
@@ -1647,12 +1646,12 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>{"tag": "metal", "per_cell": true, "amount": 3}</t>
+          <t>{"tag": "crafted", "per_cell": true, "amount": 3}</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>获得新的金属标签道具，格子*3点</t>
+          <t>获得新的工艺标签道具，格子*3点</t>
         </is>
       </c>
       <c r="F10" s="4" t="n"/>
@@ -1733,12 +1732,12 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>{"tag": "trophy", "rarity_pow": true, "plus": 1}</t>
+          <t>{"tag": "beast_part", "rarity_pow": true, "plus": 1}</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>每局游戏中首次将一种战利品置入背包时，根据稀有度增加2^稀有度等级+1</t>
+          <t>每局游戏中首次将一种兽材置入背包时，根据稀有度增加2^稀有度等级+1</t>
         </is>
       </c>
       <c r="F13" s="4" t="n"/>
@@ -1789,7 +1788,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="13.5"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1845,12 +1844,12 @@
       </c>
       <c r="C2" s="4" t="inlineStr">
         <is>
-          <t>tags: bone</t>
+          <t>tags: beast_part</t>
         </is>
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>骨制品</t>
+          <t>兽材</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
@@ -1901,16 +1900,16 @@
       </c>
       <c r="C4" s="4" t="inlineStr">
         <is>
-          <t>tags: flesh</t>
+          <t>tags: weapon</t>
         </is>
       </c>
       <c r="D4" s="4" t="inlineStr">
         <is>
-          <t>血肉</t>
+          <t>武器</t>
         </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F4" s="4" t="b">
         <v>0</v>
@@ -1919,26 +1918,26 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>brute</t>
+          <t>sun</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>蛮神</t>
+          <t>日神</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>tags: weapon</t>
+          <t>tags: crystal</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>武器</t>
+          <t>魔晶石</t>
         </is>
       </c>
       <c r="E5" s="4" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F5" s="4" t="b">
         <v>0</v>
@@ -1957,12 +1956,12 @@
       </c>
       <c r="C6" s="4" t="inlineStr">
         <is>
-          <t>tags: metal</t>
+          <t>tags: fire</t>
         </is>
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>金属</t>
+          <t>火焰</t>
         </is>
       </c>
       <c r="E6" s="4" t="n">
@@ -1985,12 +1984,12 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>tags: fire</t>
+          <t>tags: valuable</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>火焰</t>
+          <t>贵重品</t>
         </is>
       </c>
       <c r="E7" s="4" t="n">
@@ -2013,12 +2012,12 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>tags: gem</t>
+          <t>exact_grade: 2</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>宝石</t>
+          <t>体积正好为中</t>
         </is>
       </c>
       <c r="E8" s="4" t="n">
@@ -2031,22 +2030,22 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>sun</t>
+          <t>nature</t>
         </is>
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>日神</t>
+          <t>自然之神</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>exact_grade: 2</t>
+          <t>tags: nature</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>体积正好为中</t>
+          <t>自然</t>
         </is>
       </c>
       <c r="E9" s="4" t="n">
@@ -2069,12 +2068,12 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>tags: nature</t>
+          <t>tags: food</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>自然</t>
+          <t>食物</t>
         </is>
       </c>
       <c r="E10" s="4" t="n">
@@ -2097,12 +2096,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>tags: food</t>
+          <t>tags: armor / shield</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>食物</t>
+          <t>防具</t>
         </is>
       </c>
       <c r="E11" s="4" t="n">
@@ -2115,57 +2114,57 @@
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
         <is>
-          <t>nature</t>
+          <t>earth</t>
         </is>
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>自然之神</t>
+          <t>大地之神</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>tags: gear / armor / shield</t>
+          <t>min_cells: 9</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>防具</t>
+          <t>大及以上体积（稀有度 × 格子数）</t>
         </is>
       </c>
       <c r="E12" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F12" s="4" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
         <is>
-          <t>earth</t>
+          <t>skill</t>
         </is>
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>大地之神</t>
+          <t>技巧之神</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>min_cells: 9</t>
+          <t>tags: weapon</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>大及以上体积（稀有度 × 格子数）</t>
+          <t>武器</t>
         </is>
       </c>
       <c r="E13" s="4" t="n">
         <v>5</v>
       </c>
       <c r="F13" s="4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14">
@@ -2181,12 +2180,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>tags: metal</t>
+          <t>tags: armor / shield</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>金属</t>
+          <t>防具</t>
         </is>
       </c>
       <c r="E14" s="4" t="n">
@@ -2209,74 +2208,74 @@
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>tags: gear / armor / shield</t>
+          <t>has_stat: crit_chance</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>防具</t>
+          <t>带有暴击属性的道具</t>
         </is>
       </c>
       <c r="E15" s="4" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F15" s="4" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" t="inlineStr">
         <is>
           <t>skill</t>
         </is>
       </c>
-      <c r="B16" s="4" t="inlineStr">
+      <c r="B16" t="inlineStr">
         <is>
           <t>技巧之神</t>
         </is>
       </c>
-      <c r="C16" s="4" t="inlineStr">
-        <is>
-          <t>has_stat: crit_chance</t>
-        </is>
-      </c>
-      <c r="D16" s="4" t="inlineStr">
-        <is>
-          <t>带有暴击属性的道具</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="F16" s="4" t="b">
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>tags: crafted</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>工艺品</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>5</v>
+      </c>
+      <c r="F16" t="b">
         <v>0</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>skill</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>技巧之神</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>tags: crafted</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>工艺品</t>
-        </is>
-      </c>
-      <c r="E17" t="n">
-        <v>5</v>
-      </c>
-      <c r="F17" t="b">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>hunt</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>狩猎之神</t>
+        </is>
+      </c>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>tags: beast_part</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>兽材</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F17" s="4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2293,12 +2292,12 @@
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>tags: flesh / bone</t>
+          <t>tags: food</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>血肉/骨头</t>
+          <t>食物</t>
         </is>
       </c>
       <c r="E18" s="4" t="n">
@@ -2308,75 +2307,20 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>hunt</t>
-        </is>
-      </c>
-      <c r="B19" s="9" t="inlineStr">
-        <is>
-          <t>狩猎之神</t>
-        </is>
-      </c>
-      <c r="C19" s="4" t="inlineStr">
-        <is>
-          <t>tags: trophy</t>
-        </is>
-      </c>
-      <c r="D19" s="4" t="inlineStr">
-        <is>
-          <t>战利品</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F19" s="4" t="b">
-        <v>0</v>
-      </c>
-    </row>
+    <row r="19"/>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>hunt</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>狩猎之神</t>
-        </is>
-      </c>
-      <c r="C20" s="4" t="inlineStr">
-        <is>
-          <t>tags: leather</t>
-        </is>
-      </c>
-      <c r="D20" s="4" t="inlineStr">
-        <is>
-          <t>皮革</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>5</v>
-      </c>
-      <c r="F20" s="4" t="b">
-        <v>0</v>
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>备注:献祭只能提升当前激活神明的信力，比如激活日神时献祭魔晶石无法提升技巧之神的信力</t>
+        </is>
+      </c>
+      <c r="C20" s="8" t="inlineStr">
+        <is>
+          <t>备注2：当一个献祭道具符合当前神明的多个tag时，同时获得多次信力。比如道具拥有兽材+武器tag，献祭给蛮神获得（稀有度*5+稀有度*2）点信力</t>
+        </is>
       </c>
     </row>
     <row r="21" ht="81" customHeight="1"/>
-    <row r="22">
-      <c r="B22" s="8" t="inlineStr">
-        <is>
-          <t>备注:献祭只能提升当前激活神明的信力，比如激活日神时献祭金属无法提升技巧之神的信力</t>
-        </is>
-      </c>
-      <c r="C22" s="8" t="inlineStr">
-        <is>
-          <t>备注2：当一个献祭道具符合当前神明的多个tag时，同时获得多次信力。比如道具拥有骨制品+武器tag，献祭给蛮神获得（稀有度*5+稀有度*2）点信力</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3204,12 +3148,12 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>{"by_type": {"battle": ["weapon"], "elite": ["gear", "armor", "shield"], "event": ["sigil", "part"], "extract": [], "core": ["treasure"]}}</t>
+          <t>{"by_type": {"battle": ["weapon"], "elite": ["armor", "shield"], "event": ["trinket", "material"], "extract": [], "core": ["valuable"]}}</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>头一回踩上一个点得到对应类型的道具（进暂存区）：战斗 → 武器；精英 → 防具；事件 → 符号 / 零件；撤离点 → 随机；BOSS → 珍宝</t>
+          <t>头一回踩上一个点得到对应类型的道具（进暂存区）：战斗 → 武器；精英 → 防具；事件 → 饰物 / 素材；撤离点 → 随机；BOSS → 贵重品</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -3535,7 +3479,7 @@
       </c>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>信物（faith_anchor）</t>
+          <t>信物（带 faith:&lt;神&gt; 即是，250）</t>
         </is>
       </c>
       <c r="F1" s="3" t="inlineStr">
@@ -3636,7 +3580,7 @@
       </c>
       <c r="E4" s="4" t="inlineStr">
         <is>
-          <t>否</t>
+          <t>是</t>
         </is>
       </c>
       <c r="F4" s="4" t="inlineStr">
@@ -3887,7 +3831,6 @@
         </is>
       </c>
     </row>
-    <row r="12"/>
     <row r="13" ht="27" customHeight="1">
       <c r="A13" s="6" t="inlineStr">
         <is>
@@ -3977,7 +3920,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>tags: metal</t>
+          <t>tags: weapon / armor / shield</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -4014,7 +3957,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>tags: gear / armor / shield / nature</t>
+          <t>tags: armor / shield / nature</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
